--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136691236</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136691288</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>136691307</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136691326</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136691079</v>
       </c>
       <c r="B10" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136691236</v>
+        <v>136923097</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>93437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,27 +1146,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716653</v>
+        <v>716578</v>
       </c>
       <c r="R6" t="n">
-        <v>7213679</v>
+        <v>7213655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på en sälg</t>
+          <t>under en gammal tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,13 +1244,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691236</t>
+          <t>https://artportalen.se/Sighting/136923097</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136691288</v>
+        <v>136691236</v>
       </c>
       <c r="B7" t="n">
         <v>80591</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716591</v>
+        <v>716653</v>
       </c>
       <c r="R7" t="n">
-        <v>7213709</v>
+        <v>7213679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,16 +1359,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691288</t>
+          <t>https://artportalen.se/Sighting/136691236</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136691307</v>
+        <v>136691288</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,31 +1376,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716525</v>
+        <v>716591</v>
       </c>
       <c r="R8" t="n">
-        <v>7213725</v>
+        <v>7213709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på en sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,6 +1456,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1474,13 +1474,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691307</t>
+          <t>https://artportalen.se/Sighting/136691288</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136691326</v>
+        <v>136691307</v>
       </c>
       <c r="B9" t="n">
         <v>58008</v>
@@ -1513,7 +1513,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716532</v>
+        <v>716525</v>
       </c>
       <c r="R9" t="n">
-        <v>7213701</v>
+        <v>7213725</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,14 +1563,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1589,16 +1589,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691326</t>
+          <t>https://artportalen.se/Sighting/136691307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136691079</v>
+        <v>136691326</v>
       </c>
       <c r="B10" t="n">
-        <v>58112</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,16 +1606,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1626,7 +1626,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1634,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716671</v>
+        <v>716532</v>
       </c>
       <c r="R10" t="n">
-        <v>7213706</v>
+        <v>7213701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,14 +1678,14 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 individer observerade på nära håll</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1699,6 +1703,117 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136691326</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136691079</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>716671</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7213706</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 individer observerade på nära håll</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136691079</t>
         </is>
@@ -1715,6 +1830,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136923097</v>
       </c>
       <c r="B6" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136691236</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>136691288</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136923097</v>
       </c>
       <c r="B6" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136691236</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>136691288</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136923097</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136691236</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>136691288</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136691037</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136691336</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136923097</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136691037</v>
+        <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>91132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716653</v>
+        <v>716646</v>
       </c>
       <c r="R4" t="n">
-        <v>7213638</v>
+        <v>7213642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,17 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>vit mycelmatta under</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691037</t>
+          <t>https://artportalen.se/Sighting/137148649</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136691336</v>
+        <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>91132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716580</v>
+        <v>716532</v>
       </c>
       <c r="R5" t="n">
-        <v>7213629</v>
+        <v>7213617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>vit mycelmatta under</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,16 +1119,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691336</t>
+          <t>https://artportalen.se/Sighting/137148664</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136923097</v>
+        <v>136691037</v>
       </c>
       <c r="B6" t="n">
-        <v>93448</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716578</v>
+        <v>716653</v>
       </c>
       <c r="R6" t="n">
-        <v>7213655</v>
+        <v>7213638</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>under en gammal tallåga</t>
+          <t>vit mycelmatta under</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136923097</t>
+          <t>https://artportalen.se/Sighting/136691037</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136691236</v>
+        <v>136691336</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,27 +1251,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1292,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716653</v>
+        <v>716580</v>
       </c>
       <c r="R7" t="n">
-        <v>7213679</v>
+        <v>7213629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1322,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på en sälg</t>
+          <t>vit mycelmatta under</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,16 +1349,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691236</t>
+          <t>https://artportalen.se/Sighting/136691336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136691288</v>
+        <v>136923097</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>93452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,27 +1366,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716591</v>
+        <v>716578</v>
       </c>
       <c r="R8" t="n">
-        <v>7213709</v>
+        <v>7213655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1437,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på en sälg</t>
+          <t>under en gammal tallåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,16 +1464,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691288</t>
+          <t>https://artportalen.se/Sighting/136923097</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136691307</v>
+        <v>136691236</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,31 +1481,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1523,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716525</v>
+        <v>716653</v>
       </c>
       <c r="R9" t="n">
-        <v>7213725</v>
+        <v>7213679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1552,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,6 +1561,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,16 +1579,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691307</t>
+          <t>https://artportalen.se/Sighting/136691236</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136691326</v>
+        <v>136691288</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,31 +1596,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1638,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716532</v>
+        <v>716591</v>
       </c>
       <c r="R10" t="n">
-        <v>7213701</v>
+        <v>7213709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,15 +1667,16 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>på en sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1704,44 +1694,47 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691326</t>
+          <t>https://artportalen.se/Sighting/136691288</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136691079</v>
+        <v>137148625</v>
       </c>
       <c r="B11" t="n">
-        <v>58112</v>
+        <v>80605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1749,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716671</v>
+        <v>716687</v>
       </c>
       <c r="R11" t="n">
-        <v>7213706</v>
+        <v>7213638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,17 +1772,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 individer observerade på nära håll</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,6 +1786,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1814,6 +1803,577 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148625</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136691307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>716525</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7213725</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136691307</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136691326</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>716532</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7213701</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på två granar</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136691326</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137148577</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>716425</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7213702</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148577</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137148593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>716682</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7213581</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>bohål i asp, kan vara gjort av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148593</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136691079</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>716671</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7213706</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3 individer observerade på nära håll</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136691079</t>
         </is>
@@ -1831,6 +2391,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136691037</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136691336</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136923097</v>
       </c>
       <c r="B8" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136691236</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136691288</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137148625</v>
       </c>
       <c r="B11" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136691037</v>
+        <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,44 +1136,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Berguvberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716653</v>
+        <v>716741</v>
       </c>
       <c r="R6" t="n">
-        <v>7213638</v>
+        <v>7213614</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,17 +1190,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vit mycelmatta under</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,34 +1214,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691037</t>
+          <t>https://artportalen.se/Sighting/137234113</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136691336</v>
+        <v>136691037</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716580</v>
+        <v>716653</v>
       </c>
       <c r="R7" t="n">
-        <v>7213629</v>
+        <v>7213638</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,16 +1346,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691336</t>
+          <t>https://artportalen.se/Sighting/136691037</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136923097</v>
+        <v>136691336</v>
       </c>
       <c r="B8" t="n">
-        <v>93454</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716578</v>
+        <v>716580</v>
       </c>
       <c r="R8" t="n">
-        <v>7213655</v>
+        <v>7213629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1434,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>under en gammal tallåga</t>
+          <t>vit mycelmatta under</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,16 +1461,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136923097</t>
+          <t>https://artportalen.se/Sighting/136691336</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136691236</v>
+        <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,44 +1478,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Berguvberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716653</v>
+        <v>716436</v>
       </c>
       <c r="R9" t="n">
-        <v>7213679</v>
+        <v>7213687</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,17 +1532,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på en sälg</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,34 +1556,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691236</t>
+          <t>https://artportalen.se/Sighting/137234107</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136691288</v>
+        <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,27 +1590,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1627,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716591</v>
+        <v>716578</v>
       </c>
       <c r="R10" t="n">
-        <v>7213709</v>
+        <v>7213655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1661,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på en sälg</t>
+          <t>under en gammal tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,38 +1688,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691288</t>
+          <t>https://artportalen.se/Sighting/136923097</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137148625</v>
+        <v>136691236</v>
       </c>
       <c r="B11" t="n">
-        <v>80608</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716687</v>
+        <v>716653</v>
       </c>
       <c r="R11" t="n">
-        <v>7213638</v>
+        <v>7213679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,12 +1766,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på en sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,16 +1803,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137148625</t>
+          <t>https://artportalen.se/Sighting/136691236</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136691307</v>
+        <v>136691288</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,31 +1820,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1853,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716525</v>
+        <v>716591</v>
       </c>
       <c r="R12" t="n">
-        <v>7213725</v>
+        <v>7213709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1891,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på en sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,6 +1900,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1919,48 +1918,47 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691307</t>
+          <t>https://artportalen.se/Sighting/136691288</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136691326</v>
+        <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>80621</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1968,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716532</v>
+        <v>716687</v>
       </c>
       <c r="R13" t="n">
-        <v>7213701</v>
+        <v>7213638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,25 +1996,21 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>barksprätt på två granar</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2034,16 +2028,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136691326</t>
+          <t>https://artportalen.se/Sighting/137148625</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137148577</v>
+        <v>136691307</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2083,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716425</v>
+        <v>716525</v>
       </c>
       <c r="R14" t="n">
-        <v>7213702</v>
+        <v>7213725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,12 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2149,16 +2143,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137148577</t>
+          <t>https://artportalen.se/Sighting/136691307</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137148593</v>
+        <v>136691326</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2182,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2198,10 +2192,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716682</v>
+        <v>716532</v>
       </c>
       <c r="R15" t="n">
-        <v>7213581</v>
+        <v>7213701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,17 +2222,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>bohål i asp, kan vara gjort av tretåig hackspett</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,16 +2258,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137148593</t>
+          <t>https://artportalen.se/Sighting/136691326</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136691079</v>
+        <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58112</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,16 +2275,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2301,7 +2295,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2309,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716671</v>
+        <v>716425</v>
       </c>
       <c r="R16" t="n">
-        <v>7213706</v>
+        <v>7213702</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,17 +2337,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>3 individer observerade på nära håll</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,6 +2372,232 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148577</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137148593</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>716682</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7213581</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bohål i asp, kan vara gjort av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148593</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136691079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58125</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Berguvberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>716671</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7213706</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 individer observerade på nära håll</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136691079</t>
         </is>
@@ -2396,6 +2620,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136691037</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136691336</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>136691236</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136691288</v>
       </c>
       <c r="B12" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136691307</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136691326</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>137148593</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>136691079</v>
       </c>
       <c r="B18" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -2065,11 +2065,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2180,11 +2176,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2295,11 +2287,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2410,11 +2398,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136691060</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136691198</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136691037</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136691336</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137148593</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137148593</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137148593</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136923097</v>
       </c>
       <c r="B10" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35138-2026 artfynd.xlsx
+++ b/artfynd/A 35138-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137148649</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137148664</v>
       </c>
       <c r="B5" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137234113</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137234107</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137148625</v>
       </c>
       <c r="B13" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137148577</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137148593</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
